--- a/docs/sprint-backlog.xlsx
+++ b/docs/sprint-backlog.xlsx
@@ -762,6 +762,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
@@ -890,6 +891,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
@@ -1077,7 +1079,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>As a Finance Officer, I want to edit disputed pending charges, void incorrect invoices, and refund paid charges, so that billing errors can be corrected at any stage.</t>
+          <t>As a Finance Officer, I want to edit disputed pending charges, void incorrect invoices, and refund paid charges, so that billing errors can be corrected while the case is open.</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -1094,7 +1096,7 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>As an Associate, I want to close an active case with a final resolution status, so that completed cases are officially closed.</t>
+          <t>As an Associate, I want to close an active case with a final resolution status, so that completed cases are officially closed once all of their billing is settled.</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -1103,6 +1105,7 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36" ht="22.5" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
@@ -1137,7 +1140,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>As a Partner, I want to reassign the Associate or Paralegal on a consultation or case, so that staffing can be corrected after the fact.</t>
+          <t>As a Partner, I want to reassign the Associate or Paralegal on a consultation before its case is opened or on an open case, so that staffing can be corrected after the fact.</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">

--- a/docs/sprint-backlog.xlsx
+++ b/docs/sprint-backlog.xlsx
@@ -668,7 +668,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>As a Client, I want to submit a consultation request with legal issue details and track its status and consultation meeting, so that the firm can evaluate my legal matter and I know where it stands.</t>
+          <t>As a Client, I want to request a consultation with legal issue details and track its status and consultation meeting, so that the firm can evaluate my legal matter and I know where it stands.</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>As a Client Relations Officer, I want to submit walk-in clients' consultation requests and follow them and their scheduled consultation meetings, so that a Partner can perform a conflict check.</t>
+          <t>As a Client Relations Officer, I want to request consultations for walk-in clients and follow them and their scheduled consultation meetings, so that a Partner can perform a conflict check.</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
